--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>88728</v>
+        <v>91343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,37 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R4" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,13 +959,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -979,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>88728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R5" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,9 +1057,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>88729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,40 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R4" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,9 +956,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -978,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B5" t="n">
-        <v>88729</v>
+        <v>91344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,37 +990,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R5" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,13 +1061,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127287489</v>
       </c>
       <c r="B4" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127321829</v>
       </c>
       <c r="B5" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>127321804</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127321900</v>
       </c>
       <c r="B7" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127287005</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127287003</v>
       </c>
       <c r="B11" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>127321918</v>
       </c>
       <c r="B14" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>127321924</v>
       </c>
       <c r="B15" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127321930</v>
       </c>
       <c r="B16" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>127290652</v>
       </c>
       <c r="B18" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>88733</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,37 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R4" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,13 +959,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -979,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>88733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R5" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,9 +1057,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>88735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,40 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R4" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,9 +956,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -978,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B5" t="n">
-        <v>88733</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,37 +990,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R5" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,13 +1061,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,7 +1083,7 @@
         <v>127321804</v>
       </c>
       <c r="B6" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127321900</v>
       </c>
       <c r="B7" t="n">
-        <v>75147</v>
+        <v>75149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127287005</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127287003</v>
       </c>
       <c r="B11" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>127321918</v>
       </c>
       <c r="B14" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>127321924</v>
       </c>
       <c r="B15" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127321930</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>127290652</v>
       </c>
       <c r="B18" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -1694,7 +1694,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127286967</v>
+        <v>127287135</v>
       </c>
       <c r="B12" t="n">
         <v>91350</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450354</v>
+        <v>450204</v>
       </c>
       <c r="R12" t="n">
-        <v>7085730</v>
+        <v>7085746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127287135</v>
+        <v>127286967</v>
       </c>
       <c r="B13" t="n">
         <v>91350</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450204</v>
+        <v>450354</v>
       </c>
       <c r="R13" t="n">
-        <v>7085746</v>
+        <v>7085730</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>88735</v>
+        <v>91356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,37 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R4" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,13 +959,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -979,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>88741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R5" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,9 +1057,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127287135</v>
+        <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450204</v>
+        <v>450354</v>
       </c>
       <c r="R12" t="n">
-        <v>7085746</v>
+        <v>7085730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127286967</v>
+        <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450354</v>
+        <v>450204</v>
       </c>
       <c r="R13" t="n">
-        <v>7085730</v>
+        <v>7085746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>88744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,40 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R4" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,9 +956,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -978,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B5" t="n">
-        <v>88741</v>
+        <v>91359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,37 +990,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R5" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,13 +1061,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,7 +1083,7 @@
         <v>127321804</v>
       </c>
       <c r="B6" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127321900</v>
       </c>
       <c r="B7" t="n">
-        <v>75149</v>
+        <v>75152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127287005</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127287003</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>127321918</v>
       </c>
       <c r="B14" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>127321924</v>
       </c>
       <c r="B15" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127321930</v>
       </c>
       <c r="B16" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>127290652</v>
       </c>
       <c r="B18" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127287489</v>
+        <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>88744</v>
+        <v>91367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,37 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450019</v>
+        <v>449736</v>
       </c>
       <c r="R4" t="n">
-        <v>7085678</v>
+        <v>7085853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,13 +959,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bördig, lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -979,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>91359</v>
+        <v>88752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R5" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,9 +1057,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,7 +1083,7 @@
         <v>127321804</v>
       </c>
       <c r="B6" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127321900</v>
       </c>
       <c r="B7" t="n">
-        <v>75152</v>
+        <v>75158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127287005</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127287003</v>
       </c>
       <c r="B11" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>127321918</v>
       </c>
       <c r="B14" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>127321924</v>
       </c>
       <c r="B15" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127321930</v>
       </c>
       <c r="B16" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>127290652</v>
       </c>
       <c r="B18" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127321868</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127321829</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127287489</v>
       </c>
       <c r="B5" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>127286967</v>
       </c>
       <c r="B12" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127287135</v>
       </c>
       <c r="B13" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>127321944</v>
       </c>
       <c r="B17" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127321863</v>
       </c>
       <c r="B2" t="n">
-        <v>91351</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127321868</v>
+        <v>127287458</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449656</v>
+        <v>450084</v>
       </c>
       <c r="R3" t="n">
-        <v>7085674</v>
+        <v>7085602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,9 +855,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -877,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127321829</v>
+        <v>127287489</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,40 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449736</v>
+        <v>450019</v>
       </c>
       <c r="R4" t="n">
-        <v>7085853</v>
+        <v>7085678</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,9 +957,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bördig, lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -978,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127287489</v>
+        <v>127287557</v>
       </c>
       <c r="B5" t="n">
-        <v>88754</v>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450019</v>
+        <v>449976</v>
       </c>
       <c r="R5" t="n">
-        <v>7085678</v>
+        <v>7085638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1064,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, lövrik grannaturskog</t>
+          <t>Luckig, lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1080,38 +1082,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127321804</v>
+        <v>127321900</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1119,13 +1120,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449882</v>
+        <v>449532</v>
       </c>
       <c r="R6" t="n">
-        <v>7085761</v>
+        <v>7085561</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,6 +1166,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Luckig grannaturskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1181,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127321900</v>
+        <v>127321804</v>
       </c>
       <c r="B7" t="n">
-        <v>75158</v>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,26 +1198,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1219,13 +1226,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449532</v>
+        <v>449882</v>
       </c>
       <c r="R7" t="n">
-        <v>7085561</v>
+        <v>7085761</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,11 +1272,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Luckig grannaturskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1289,7 +1291,7 @@
         <v>127286863</v>
       </c>
       <c r="B8" t="n">
-        <v>98492</v>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1393,7 @@
         <v>127287059</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,11 +1495,11 @@
         <v>127287005</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1595,7 +1597,7 @@
         <v>127287003</v>
       </c>
       <c r="B11" t="n">
-        <v>75153</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127286967</v>
+        <v>127321918</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,34 +1707,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450354</v>
+        <v>449503</v>
       </c>
       <c r="R12" t="n">
-        <v>7085730</v>
+        <v>7085535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig, lövrik grannaturskog</t>
+          <t>Luckig grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127287135</v>
+        <v>127321924</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,34 +1812,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450204</v>
+        <v>449503</v>
       </c>
       <c r="R13" t="n">
-        <v>7085746</v>
+        <v>7085535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig, lövrik grannaturskog</t>
+          <t>Luckig grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1898,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127321918</v>
+        <v>127321944</v>
       </c>
       <c r="B14" t="n">
-        <v>79108</v>
+        <v>89292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,21 +1917,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449503</v>
+        <v>449392</v>
       </c>
       <c r="R14" t="n">
-        <v>7085535</v>
+        <v>7085332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127321924</v>
+        <v>127321930</v>
       </c>
       <c r="B15" t="n">
-        <v>82870</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449503</v>
+        <v>449570</v>
       </c>
       <c r="R15" t="n">
-        <v>7085535</v>
+        <v>7085419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127321930</v>
+        <v>127290652</v>
       </c>
       <c r="B16" t="n">
-        <v>80133</v>
+        <v>58057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,40 +2127,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodrun, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449570</v>
+        <v>450422</v>
       </c>
       <c r="R16" t="n">
-        <v>7085419</v>
+        <v>7085479</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2195,7 +2200,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Luckig grannaturskog</t>
+          <t>Luckig, lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2210,213 +2215,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127321944</v>
-      </c>
-      <c r="B17" t="n">
-        <v>88754</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>510</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bodrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>449392</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7085332</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Luckig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127290652</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57776</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bodrun, Bodrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>450422</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7085479</v>
-      </c>
-      <c r="S18" t="n">
-        <v>30</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61388-2024 artfynd.xlsx
+++ b/artfynd/A 61388-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287458</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321900</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321804</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127286863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287059</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287005</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127287003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321918</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321924</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321944</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127321930</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,8 +2290,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127290652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>